--- a/data/payments.xlsx
+++ b/data/payments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,6 @@
           <t>Umashankar Pradhan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>5000</v>
       </c>
@@ -509,8 +508,50 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Umashankar Pradhan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>

--- a/data/payments.xlsx
+++ b/data/payments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,90 +470,6 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Umashankar Pradhan</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>800</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4200</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Umashankar Pradhan</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Partial</t>
         </is>
       </c>
     </row>
